--- a/human_validation/judge/kor/judge_D015_S001_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D015_S001_P003__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,187 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요. 오늘 저를 찾아오신 이유가 무엇인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 아버지가 쇠약해지도록 내버려둔 것에 대해 벌을 받고 있다는 느낌을 떨쳐낼 수가 없어서 왔어요. 언니가 의사 소견서를 보여주면서 제가 할 수 있는 건 다 했다고 말해주지만... 그게 바뀌지는 않아요. 마치 이미 저에 대한 어떤 판결이 내려진 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 느낌들과 함께, 대부분의 날에 지속적으로 가라앉거나 슬프거나 절망적인 느낌을 받으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 대부분의 날에 무겁고 텅 빈 느낌으로 잠에서 깨요, 마치 모든 색이 다 빠져나간 것처럼요. 회사 책상에 있거나 정원을 보고 있을 때도, 그냥... 아무것도 저한테 와닿지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 며칠 이상 이어지는 기간 동안 비정상적으로 활력이 넘치거나 들뜨거나, 잠을 훨씬 덜 필요로 했던 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 그런 것 같지 않아요. 비정상적으로 활력이 넘치거나 잠을 훨씬 덜 필요로 했던 시기가 기억이 안 나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이번처럼 가라앉거나 우울한 느낌을 살면서 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 힘든 시기는 있었지만, 이번과 같았는지는 말씀드리기 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 다른 사람들에게는 들리지 않는 목소리나 소리를 들으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네. 집이 조용해지는 밤이면 가끔 여자 목소리가 들려요, 마치 복도에 있는 것처럼요, "넌 그를 실망시켰어"라고 말하는 것 같은. 확인하려고 몇 번이나 일어났는데, 아무도 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 과거의 그 힘든 시기 동안, 우울증 때문에 전문가의 도움을 받거나 약을 복용하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 그때 누군가를 찾아갔거나 뭔가를 복용했던 기억은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 과거의 그 힘든 시기 동안, 침대에서 일어나거나 일상적인 책임을 수행하기 힘들었던 2주 이상의 기간이 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네... 회사에서 마감을 놓치고 평소 같으면 처리했을 직원 회의를 피한 적이 있어요. 도서관 자원봉사도 안 나가게 됐어요, 제 자신을 꾸준히 유지할 수가 없어서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 지금 겪고 계신 이 삽화 전에, 이런 식의 우울증을 겪었던 별개의 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 지금과 같은 별개의 시기는 딱히 떠오르지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>진단명: 정신병적 양상을 동반한 주요우울장애 (D015)
 인구통계: 성별 여성 / 나이 46 / 직업상태 human resources worker / 최종학력 학사
@@ -575,245 +747,40 @@
 증상 지속 기간: None
 추가 요건: delusions_and_hallucinations occur exclusively during the major depressive episode
 주호소 증상 코드: S019
-배경 서술: 샤론의 세심하게 균형 잡힌 삶은 홀아버지의 건강과 행동이 악화되면서 바뀌었는데, 이는 그녀의 인사 업무 위에 잦은 전화, 진료 예약, 친척들 사이의 갈등 중재까지 더해지게 만들었다. 1년 2개월에 걸쳐, 늘어난 돌봄 부담이 그녀의 정원 가꾸기, 탐조, 도서관 자원봉사, 그리고 조용히 재충전하던 일상들을 밀어냈고, 그녀는 수면 장애, 눈에 띄는 행동 둔화, 아버지를 위해 내리는 모든 결정에 대한 과도한 죄책감을 동반한 지속적인 우울한 기분을 겪게 되었다. 삽화가 진행되면서 그녀의 죄책감은 자신이 가족을 실망시킨 것에 대해 벌을 받고 있다는 고정된 믿음으로 굳어졌고, 생생한 지각과 유사한 경험들을 동반했으며, 죽음에 대한 반복적인 생각이 직장에서의 신뢰성에 영향을 미치기 시작했다. 그녀는 직원 중재 도중 무너져 내리며 지금까지 벌어진 일의 기간과 강도를 털어놓았고, 이를 계기로 산업보건 의뢰가 마련되면서 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요. 오늘 저를 찾아오신 이유가 무엇인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 아버지가 쇠약해지도록 내버려둔 것에 대해 벌을 받고 있다는 느낌을 떨쳐낼 수가 없어서 왔어요. 언니가 의사 소견서를 보여주면서 제가 할 수 있는 건 다 했다고 말해주지만... 그게 바뀌지는 않아요. 마치 이미 저에 대한 어떤 판결이 내려진 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 느낌들과 함께, 대부분의 날에 지속적으로 가라앉거나 슬프거나 절망적인 느낌을 받으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 대부분의 날에 무겁고 텅 빈 느낌으로 잠에서 깨요, 마치 모든 색이 다 빠져나간 것처럼요. 회사 책상에 있거나 정원을 보고 있을 때도, 그냥... 아무것도 저한테 와닿지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 며칠 이상 이어지는 기간 동안 비정상적으로 활력이 넘치거나 들뜨거나, 잠을 훨씬 덜 필요로 했던 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 그런 것 같지 않아요. 비정상적으로 활력이 넘치거나 잠을 훨씬 덜 필요로 했던 시기가 기억이 안 나요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이번처럼 가라앉거나 우울한 느낌을 살면서 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 힘든 시기는 있었지만, 이번과 같았는지는 말씀드리기 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 다른 사람들에게는 들리지 않는 목소리나 소리를 들으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네. 집이 조용해지는 밤이면 가끔 여자 목소리가 들려요, 마치 복도에 있는 것처럼요, "넌 그를 실망시켰어"라고 말하는 것 같은. 확인하려고 몇 번이나 일어났는데, 아무도 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 과거의 그 힘든 시기 동안, 우울증 때문에 전문가의 도움을 받거나 약을 복용하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 그때 누군가를 찾아갔거나 뭔가를 복용했던 기억은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 과거의 그 힘든 시기 동안, 침대에서 일어나거나 일상적인 책임을 수행하기 힘들었던 2주 이상의 기간이 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네... 회사에서 마감을 놓치고 평소 같으면 처리했을 직원 회의를 피한 적이 있어요. 도서관 자원봉사도 안 나가게 됐어요, 제 자신을 꾸준히 유지할 수가 없어서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 지금 겪고 계신 이 삽화 전에, 이런 식의 우울증을 겪었던 별개의 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 지금과 같은 별개의 시기는 딱히 떠오르지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
+배경 서술: 샤론의 세심하게 균형 잡힌 삶은 홀아버지의 건강과 행동이 악화되면서 바뀌었는데, 이는 그녀의 인사 업무 위에 잦은 전화, 진료 예약, 친척들 사이의 갈등 중재까지 더해지게 만들었다. 1년 2개월에 걸쳐, 늘어난 돌봄 부담이 그녀의 정원 가꾸기, 탐조, 도서관 자원봉사, 그리고 조용히 재충전하던 일상들을 밀어냈고, 그녀는 수면 장애, 눈에 띄는 행동 둔화, 아버지를 위해 내리는 모든 결정에 대한 과도한 죄책감을 동반한 지속적인 우울한 기분을 겪게 되었다. 삽화가 진행되면서 그녀의 죄책감은 자신이 가족을 실망시킨 것에 대해 벌을 받고 있다는 고정된 믿음으로 굳어졌고, 생생한 지각과 유사한 경험들을 동반했으며, 죽음에 대한 반복적인 생각이 직장에서의 신뢰성에 영향을 미치기 시작했다. 그녀는 직원 중재 도중 무너져 내리며 지금까지 벌어진 일의 기간과 강도를 털어놓았고, 이를 계기로 산업보건 의뢰가 마련되면서 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+        </is>
+      </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 정신병적 양상을 동반한 주요우울장애 (D015, ICD: F32.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=2, 커버리지=0.4)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
-  누락: 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 정신병적 양상을 동반한 주요우울장애 (D015, ICD: F32.3)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=2, 커버리지=0.4)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D015_S001_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D015_S001_P003__gemini-3.8-flash_kor.xlsx
@@ -733,6 +733,11 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -776,11 +781,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D015_S001_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D015_S001_P003__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1975</v>
+        <v>0.3437</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.9375</v>
+        <v>0.7292</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.2079</v>
+        <v>0.4791</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.25</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
